--- a/fmt/tests/bank_isabel_demo.xlsx
+++ b/fmt/tests/bank_isabel_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedric\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619B780E-977C-4EB7-923D-0E333E007F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38732C04-8989-4118-80FA-FBBD5471A327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="165" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
     <t>05-000000066</t>
   </si>
   <si>
-    <t>+++000/0000/00202+++</t>
+    <t>+++700/0000/00202+++</t>
   </si>
 </sst>
 </file>
@@ -193,12 +193,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,7 +714,7 @@
       <c r="S2" t="s">
         <v>32</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="U2" t="s">
@@ -802,7 +803,7 @@
       <c r="S3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="U3" t="s">

--- a/fmt/tests/bank_isabel_demo.xlsx
+++ b/fmt/tests/bank_isabel_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38732C04-8989-4118-80FA-FBBD5471A327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B375AF-F124-40B4-9A90-61F76467AA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="765" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,7 +154,7 @@
     <t>05-000000066</t>
   </si>
   <si>
-    <t>+++700/0000/00202+++</t>
+    <t>+++700/0000/00246+++</t>
   </si>
 </sst>
 </file>

--- a/fmt/tests/bank_isabel_demo.xlsx
+++ b/fmt/tests/bank_isabel_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B375AF-F124-40B4-9A90-61F76467AA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FA6880-7ACB-47A4-AA0A-24D0C82B8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="765" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,7 +154,7 @@
     <t>05-000000066</t>
   </si>
   <si>
-    <t>+++700/0000/00246+++</t>
+    <t>+++700/0000/00145+++</t>
   </si>
 </sst>
 </file>
